--- a/data/New Dataset/python-codes-labeled.xlsx
+++ b/data/New Dataset/python-codes-labeled.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,42 +417,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>srp</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ocp</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>lsp</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>isp</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>dip</t>
         </is>
@@ -1021,11 +1009,31 @@
 print(total_area(shapes))</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1058,11 +1066,31 @@
         self.service.send_notification(message)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/data/New Dataset/python-codes-labeled.xlsx
+++ b/data/New Dataset/python-codes-labeled.xlsx
@@ -1133,11 +1133,31 @@
         self.food.eat()        </t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1171,11 +1191,31 @@
 find_red_cars(cars)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1210,11 +1250,31 @@
 find_red_cars(cars)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1262,11 +1322,31 @@
 payment_processor.pay_credit(order, security_code)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1356,11 +1436,31 @@
     </t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1398,11 +1498,31 @@
         order.status = "paid"</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1448,11 +1568,31 @@
         return self.operations[operator].execute(a, b)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1502,11 +1642,31 @@
 payment_processor.process_payment("crypto", 200)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1584,11 +1744,31 @@
 print(order.status)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1620,11 +1800,31 @@
 print(cat.get_sound())</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1673,11 +1873,31 @@
     print(rock_songs.get_upper_case_title())</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1728,11 +1948,31 @@
 Analysis(team_memberships)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1839,11 +2079,31 @@
     app.run(debug=True)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1897,11 +2157,31 @@
     print("Sorted Data:", sorted_data)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1941,11 +2221,31 @@
 </t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1994,11 +2294,31 @@
     print(rock_songs.get_upper_case_title())</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2153,11 +2473,31 @@
         print(f"Payment failed and PaymentProcessor raised an exception: {e}")</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2220,11 +2560,31 @@
     car.speed_control.accelerate()</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2251,11 +2611,31 @@
         pass</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2342,11 +2722,31 @@
     main()</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2384,11 +2784,31 @@
 consumer2.consume_content()</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2438,11 +2858,31 @@
         self.studentId = studentId</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2504,11 +2944,31 @@
 </t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2543,11 +3003,31 @@
             archive.extractall()</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2610,11 +3090,31 @@
 </t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2646,11 +3146,31 @@
 </t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2691,11 +3211,31 @@
             print("We have {} in our shop.".format(album_name))</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2757,11 +3297,31 @@
     car.speed_control.accelerate()</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2794,11 +3354,31 @@
         return self.side ** 2</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2838,11 +3418,31 @@
     print(tesla.start_engine())</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2930,11 +3530,31 @@
         return super().get_discount() * 2</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2988,11 +3608,31 @@
 </t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3038,11 +3678,31 @@
 print(duck.quack())</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3081,11 +3741,31 @@
 user.otp_send(user.set_otp())</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3118,11 +3798,31 @@
         return X + y</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3256,11 +3956,31 @@
         print(f"Error con el procesamiento: {e}")</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3539,11 +4259,31 @@
     )</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3584,11 +4324,31 @@
     print("manager fails to support super_worker....")</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3663,11 +4423,31 @@
     print("\n")</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3714,11 +4494,31 @@
         auth.authorize()</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3765,11 +4565,31 @@
 </t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">

--- a/data/New Dataset/python-codes-labeled.xlsx
+++ b/data/New Dataset/python-codes-labeled.xlsx
@@ -4619,11 +4619,31 @@
 </t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4671,11 +4691,31 @@
 TeamPlayersList(team_players)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4705,11 +4745,31 @@
 network_writer = Writer(type=1)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4738,11 +4798,31 @@
         self.bread.eat() </t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4778,11 +4858,31 @@
 print(discount.get_discount())</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4911,11 +5011,31 @@
     cart_service.sign_out_cart()</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4957,11 +5077,31 @@
 print(printer.get_book(book, mobile_formatter))</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4993,11 +5133,31 @@
             archive.extractall()</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5061,11 +5221,31 @@
     subject.set_state("State 2")</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5108,11 +5288,31 @@
     </t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5141,11 +5341,31 @@
 </t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5187,11 +5407,31 @@
 </t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5289,11 +5529,31 @@
 pprint.pprint(student.member_schedule(hours=Hours.FEW, days=Days.FEW))</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5332,11 +5592,31 @@
 register.register(student)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5381,11 +5661,31 @@
     print(svc.service_list_user())</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5422,11 +5722,31 @@
 </t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5454,11 +5774,31 @@
 mfd.fax()</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5610,11 +5950,31 @@
 company.close()</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5649,11 +6009,31 @@
             archive.extractall()</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5689,11 +6069,31 @@
 logger.log_stderr("An error!")</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5773,11 +6173,31 @@
     print("Data loaded from database:", new_directory_data)</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5810,11 +6230,31 @@
 book.print_content()</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5933,11 +6373,31 @@
         return super().get_discount() * 2</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6007,11 +6467,31 @@
         order.status = "paid"</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6066,11 +6546,31 @@
     print(blog.list_pages())</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6145,11 +6645,31 @@
     data_manager_mysql = DataManager(mysql_database)</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6190,11 +6710,31 @@
 shoo_shoo([Eagle(), Penguin()])</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6240,11 +6780,31 @@
 </t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6277,11 +6837,31 @@
         print("logic to save to DB")</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6333,11 +6913,31 @@
 </t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6386,11 +6986,31 @@
 Research(relationships)</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6415,11 +7035,31 @@
         print(f"Sending welcome email to {self.email}.")</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6456,11 +7096,31 @@
 </t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6499,11 +7159,31 @@
 print(airplane.fly())   </t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6534,11 +7214,31 @@
 mfd.scan()</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6568,11 +7268,31 @@
         pass</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6611,11 +7331,31 @@
         print(res)</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6658,11 +7398,31 @@
     app2.start()</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6710,11 +7470,31 @@
     print(ret.get_area())</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6763,11 +7543,31 @@
 order.pay("debit", "0372846")</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6820,11 +7620,31 @@
     order.send_notification()</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6916,11 +7736,31 @@
 processor.pay(order)</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6980,11 +7820,31 @@
 """</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7032,11 +7892,31 @@
 order.pay('debit', '123123')</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7076,11 +7956,31 @@
 print(calculator.calculate(order_express))  # Output: 60.0</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7114,11 +8014,31 @@
         pass</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7158,11 +8078,31 @@
     mailer_2.send('hello!')</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7275,11 +8215,31 @@
     pass</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7339,11 +8299,31 @@
     print(staff_amany.lock_user(seller_xyz.username))</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7493,11 +8473,31 @@
         print(f"Payment failed and PaymentProcessor raised an exception: {e}")</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">

--- a/data/New Dataset/python-codes-labeled.xlsx
+++ b/data/New Dataset/python-codes-labeled.xlsx
@@ -8551,11 +8551,31 @@
 payment_processor.pay(order, security_code)</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8599,11 +8619,31 @@
     </t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8629,11 +8669,31 @@
         return "Data from the database"</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8672,11 +8732,31 @@
         self._log_file.write(f"[{self._log_source}] {log_message}")</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8713,11 +8793,31 @@
 network_writer.write(b'hello world')</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8750,11 +8850,31 @@
         return self.side ** 2</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8802,11 +8922,31 @@
         print(product.get_discount())</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8885,11 +9025,31 @@
     main()</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8948,11 +9108,31 @@
 cat.swim()</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9022,11 +9202,31 @@
         order.status = "paid"</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9173,11 +9373,31 @@
         print(f"Payment failed and PaymentProcessor raised an exception: {e}")</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9218,11 +9438,31 @@
 find_red_cars(cars)</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9262,11 +9502,31 @@
 payment_only_processor.process_payment(200)</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9302,11 +9562,31 @@
     mfcc_extractor.extract(dummy_data)</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9353,11 +9633,31 @@
 print(myTelephoneDirectory)</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -9393,11 +9693,31 @@
             print (task)</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -9426,11 +9746,31 @@
 book2 = Book("To Kill a Mockingbird", "Harper Lee")</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -9478,11 +9818,31 @@
 </t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -9521,11 +9881,31 @@
 saver.save_to_db(invoice)</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -9558,11 +9938,31 @@
         raise Exception(message)</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -9615,11 +10015,31 @@
 switch2.press()</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -9689,11 +10109,31 @@
     print(file_saver.save())</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -9728,11 +10168,31 @@
         return self.price - discount</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -9770,11 +10230,31 @@
     order.send_notification()</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -9815,11 +10295,31 @@
         print(f"Scanning {document}...")</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9855,11 +10355,31 @@
 print(animal_sound.get_sound(dog))</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9905,11 +10425,31 @@
     print(products.products)</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -9951,11 +10491,31 @@
 </t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -9994,11 +10554,31 @@
 client.play_media(photo_viewer)  </t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10037,11 +10617,31 @@
         self._log_file.write(f"[{self._log_source}] {log_message}")</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -10087,11 +10687,31 @@
 print(duck.quack())</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -10131,11 +10751,31 @@
         </t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -10182,11 +10822,31 @@
     landline.make_calls("987-654-3210")</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -10229,11 +10889,31 @@
 print_area(square)</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -10266,11 +10946,31 @@
         print(f"Saving {user.user_name} to database...")</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -10312,11 +11012,31 @@
 print_employee(prog)</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -10366,11 +11086,31 @@
 processor.credit_type(order, "0372846")</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -10406,11 +11146,31 @@
     TEXT_FILE = 2</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -10484,11 +11244,31 @@
         order.status = "paid"</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -10540,11 +11320,31 @@
 print(x.name)</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -10604,11 +11404,31 @@
     example()</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -10640,11 +11460,31 @@
 DatabaseWriter(database, Logger())</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -10700,11 +11540,31 @@
 cart.checkout(300)</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10746,11 +11606,31 @@
 notification_manager.send_notification("Hello, Kashishh")</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10790,11 +11670,31 @@
 </t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -10834,11 +11734,31 @@
             print("We have {} in our shop.".format(album_name))</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10887,11 +11807,31 @@
     print()</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10972,11 +11912,31 @@
 fighter.fight(goblin)</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Violation</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -11015,11 +11975,31 @@
 </t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -11079,11 +12059,31 @@
 cat.talk()</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">

--- a/data/New Dataset/python-codes-labeled.xlsx
+++ b/data/New Dataset/python-codes-labeled.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,42 +429,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>srp</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ocp</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lsp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>isp</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>dip</t>
         </is>
@@ -1751,7 +1763,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2729,7 +2741,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4752,7 +4764,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Violation</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6380,7 +6392,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Violation</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">

--- a/data/New Dataset/python-codes-labeled.xlsx
+++ b/data/New Dataset/python-codes-labeled.xlsx
@@ -2630,17 +2630,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2803,17 +2803,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>

--- a/data/New Dataset/python-codes-labeled.xlsx
+++ b/data/New Dataset/python-codes-labeled.xlsx
@@ -3432,22 +3432,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>Violation</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Violation</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Violation</t>
-        </is>
-      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3692,27 +3692,27 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3760,17 +3760,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4437,27 +4437,27 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>Violation</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Violation</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Violation</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Violation</t>
-        </is>
-      </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5035,12 +5035,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5091,17 +5091,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Violation</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
